--- a/outputs/evaluation/requirement/CF_M05_req_eval.xlsx
+++ b/outputs/evaluation/requirement/CF_M05_req_eval.xlsx
@@ -2130,7 +2130,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R_02b</t>
+          <t>R_02a</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2140,27 +2140,28 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The system shall grant access to the portal only if credentials are valid.</t>
+          <t>The system shall validate user credentials.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CF_M05_R01</t>
+          <t>CF_M05_R22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Access the portal using credential authentication personal.</t>
+          <t>The system must allow the creation, consultation, modification and
+data deletion for authorized users.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.7652</v>
+        <v>0.7201</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R_04</t>
+          <t>R_02b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2170,21 +2171,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The system shall only show the applications for which the user has authorized access.</t>
+          <t>The system shall grant access to the portal only if credentials are valid.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M05_R02</t>
+          <t>CF_M05_R01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>View the portal applications to which the user has access.</t>
+          <t>Access the portal using credential authentication personal.</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.773</v>
+        <v>0.7652</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/evaluation/requirement/CF_M05_req_eval.xlsx
+++ b/outputs/evaluation/requirement/CF_M05_req_eval.xlsx
@@ -448,7 +448,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.88</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="8">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9167</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="9">
@@ -558,10 +558,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9545</v>
+        <v>0.9524</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9545</v>
+        <v>0.9524</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -576,13 +576,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.88</v>
+        <v>0.913</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9167</v>
+        <v>0.875</v>
       </c>
       <c r="D15" t="n">
-        <v>0.95</v>
+        <v>0.9484</v>
       </c>
     </row>
     <row r="16">
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8333</v>
+        <v>0.8</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8333</v>
+        <v>0.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1561,20 +1561,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R_11</t>
+          <t>R_10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M05_R09</t>
+          <t>CF_M05_R08</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9832</v>
+        <v>0.9885</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1584,20 +1584,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Design, colors, fonts, and organization must be consistent with the old version.</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>R_10</t>
-        </is>
-      </c>
+          <t>The new content must maintain visual coherence with the design of the old version of the application.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>10a. Appearance</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1605,31 +1609,35 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>The design, organization, colors and typoghraphy must be consistent with the old version.</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>CF_M05_R08</t>
-        </is>
-      </c>
+          <t>The new content must maintain visual consistency with the design of the old version of the application.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>10a. Appearance</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R_10</t>
+          <t>R_22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M05_R08</t>
+          <t>CF_M05_R20</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9885</v>
+        <v>0.9937</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1638,17 +1646,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>The new content must maintain visual coherence with the design of the old version of the application.</t>
+          <t>The web application must support a large number of concurrent users without degrading its performance.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>10a. Appearance</t>
+          <t>12f. Capacity</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1664,16 +1672,17 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>The new content must maintain visual consistency with the design of the old version of the application.</t>
+          <t>The web application must support a large number of simultaneous users
+without degrading its performance.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>10a. Appearance</t>
+          <t>12f. Capacity</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1687,12 +1696,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R_22</t>
+          <t>R_19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M05_R20</t>
+          <t>CF_M05_R17</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1700,130 +1709,130 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>The web application must support a large number of concurrent users without degrading its performance.</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>12f. Capacity</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Response time must not exceed 1 second in 95% of queries.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>R_18</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>The web application must support a large number of simultaneous users
-without degrading its performance.</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>12f. Capacity</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
+          <t>Response time should not exceed 1 second in 95% of queries.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>CF_M05_R16</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R_19</t>
+          <t>R_23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M05_R17</t>
+          <t>CF_M05_R22</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9937</v>
+        <v>0.9951</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Response time must not exceed 1 second in 95% of queries.</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>R_18</t>
-        </is>
-      </c>
+          <t>The system must allow the creation, consultation, modification, and deletion of data for authorized users.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>15a. Access</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Response time should not exceed 1 second in 95% of queries.</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>CF_M05_R16</t>
-        </is>
-      </c>
+          <t>The system must allow the creation, consultation, modification and
+data deletion for authorized users.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>15a. Access</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R_23</t>
+          <t>R_20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M05_R22</t>
+          <t>CF_M05_R18</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9951</v>
+        <v>0.9973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1837,12 +1846,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>The system must allow the creation, consultation, modification, and deletion of data for authorized users.</t>
+          <t>The web application must guarantee continuous and stable operation, ensuring its availability at all times.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>15a. Access</t>
+          <t>12a. Availability</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1862,13 +1871,13 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>The system must allow the creation, consultation, modification and
-data deletion for authorized users.</t>
+          <t>The web application must guarantee continuous and stable operation,
+ensuring its availability at any time.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>15a. Access</t>
+          <t>12th. Availability</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1882,16 +1891,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R_20</t>
+          <t>R_12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M05_R18</t>
+          <t>CF_M05_R10</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9973</v>
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1900,17 +1909,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>The web application must guarantee continuous and stable operation, ensuring its availability at all times.</t>
+          <t>The system must be easy to use for any user.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>12a. Availability</t>
+          <t>11a. Ease of use</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1926,17 +1935,16 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>The web application must guarantee continuous and stable operation,
-ensuring its availability at any time.</t>
+          <t>The system must be easy to use for any user.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>12th. Availability</t>
+          <t>11a. Ease of use</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1950,12 +1958,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R_12</t>
+          <t>R_14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CF_M05_R10</t>
+          <t>CF_M05_R12</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1973,12 +1981,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>The system must be easy to use for any user.</t>
+          <t>The application must be available in multiple languages.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>11a. Ease of use</t>
+          <t>11b. Customization and internationalization</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1998,12 +2006,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>The system must be easy to use for any user.</t>
+          <t>The application must be available in multiple languages.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>11a. Ease of use</t>
+          <t>11b. Personalization and internationalization</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2013,73 +2021,6 @@
       </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>R_14</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>CF_M05_R12</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>The application must be available in multiple languages.</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>11b. Customization and internationalization</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>53</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>The application must be available in multiple languages.</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>11b. Personalization and internationalization</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2092,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2186,36 +2127,6 @@
       </c>
       <c r="F3" t="n">
         <v>0.7652</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>R_25</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>No user can access data from other clients.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CF_M05_R05</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Ensure that other customers' data cannot be accessed.</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0.8608</v>
       </c>
     </row>
   </sheetData>
@@ -2229,7 +2140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2267,7 +2178,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M05_R19</t>
+          <t>CF_M05_R09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2277,50 +2188,80 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>System availability must be at least 99.9%, even during times of intensive use.</t>
+          <t>The design, organization, colors and typoghraphy must be consistent with the old version.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>R_21</t>
+          <t>R_10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>System availability must be at least 99.9%, even during peak usage times.</t>
+          <t>The new content must maintain visual coherence with the design of the old version of the application.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.9821</v>
+        <v>0.8862</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>CF_M05_R19</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Criterion</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>System availability must be at least 99.9%, even during times of intensive use.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>R_21</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>System availability must be at least 99.9%, even during peak usage times.</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9821</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>CF_M05_R24</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Functionality for generating graphs and interactive panels that represent communication statistics, traffic volume, response times and incidents, facilitating more intuitive and faster analysis.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>The system must be easy to use for any user.</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F4" t="n">
         <v>0.6278</v>
       </c>
     </row>
